--- a/src/attributions/attributions_ig_traj_180.xlsx
+++ b/src/attributions/attributions_ig_traj_180.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3946316326473421</v>
+        <v>0.4156361622552384</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06592602029635787</v>
+        <v>0.06402614981271625</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2809196178285841</v>
+        <v>-0.3062711062396781</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1592,13 +1592,13 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.148269403920821</v>
+        <v>0.2236726671855697</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0167909340739812</v>
+        <v>-0.02798260886441799</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06130383441401731</v>
+        <v>-0.05640804838260031</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
@@ -1622,25 +1622,25 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05647182001378358</v>
+        <v>-0.1239784003852151</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.09422549560767313</v>
+        <v>-0.1191405021153036</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003942275102318556</v>
+        <v>-0.1319236355349414</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
@@ -1649,22 +1649,22 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.08567746279316305</v>
+        <v>0.1258174301418703</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1289855301294916</v>
+        <v>0.04158376180607815</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03848504557963029</v>
+        <v>0.1111561334226251</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1673,25 +1673,25 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.06737736153840614</v>
+        <v>0.1346889778897059</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.02815831131503914</v>
+        <v>-0.00449809614109023</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.1607463584730553</v>
+        <v>-0.2281554141082583</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
@@ -1703,37 +1703,37 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4380858910691841</v>
+        <v>0.6840768914964721</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1310788665910175</v>
+        <v>-0.2744150748697978</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.375077329769664</v>
+        <v>-0.3821610767677349</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1647518705808296</v>
+        <v>0.1438038280839145</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.04851117025015965</v>
+        <v>0.06016669755919993</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.1065995765996841</v>
+        <v>-0.1650289695328564</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1757,52 +1757,52 @@
         <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03007462345848597</v>
+        <v>0.04351871273202955</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.02259004500026864</v>
+        <v>0.1299989630554755</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02468364845416601</v>
+        <v>0.1453081828967192</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.148695297018421</v>
+        <v>0.2486519848476308</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.08544677695275743</v>
+        <v>-0.09605381636326868</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.09442065481909999</v>
+        <v>-0.270449917988661</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1814,7 +1814,7 @@
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1538988073826628</v>
+        <v>-0.2843767478193017</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.008681192040110097</v>
+        <v>-0.0484092980957461</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1084018586188021</v>
+        <v>0.182777093946296</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1841,52 +1841,52 @@
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.02118466379680954</v>
+        <v>-0.3407671727458096</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.035078217924226</v>
+        <v>0.06027576620501852</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.02082180164832465</v>
+        <v>0.1908684134130064</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.1318224180743149</v>
+        <v>-0.2675198146544366</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.003175587173527037</v>
+        <v>-0.04173601406468452</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.1239511785673071</v>
+        <v>0.1516830923005987</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
@@ -1895,73 +1895,73 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.04720204965234161</v>
+        <v>-0.1182732557442661</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
         <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03354403072157864</v>
+        <v>-0.06258771529569702</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.001212473509429661</v>
+        <v>0.1232611419834048</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0143555773277746</v>
+        <v>-0.1166229675682487</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.08786994297265861</v>
+        <v>-0.001568484147698277</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01597031312472365</v>
+        <v>0.04412518030836335</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.09709923504887749</v>
+        <v>0.1375167543868193</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.02930254492052927</v>
+        <v>-0.04758213706030524</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.03158669474083305</v>
+        <v>0.1288264236504922</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1973,25 +1973,25 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.1496793145813296</v>
+        <v>-0.1319644592322021</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.005435327415342472</v>
+        <v>-0.08063655104506748</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.11228485724669</v>
+        <v>0.1687352125502564</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
@@ -2000,49 +2000,49 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.09417150050969911</v>
+        <v>-0.1749318859378227</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.009751862133375139</v>
+        <v>-0.1799261069180624</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.08879479376476841</v>
+        <v>0.20791904391777</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.1430247183184711</v>
+        <v>-0.2634682752989074</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.006389788317465739</v>
+        <v>-0.1025894585445022</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1210252600750234</v>
+        <v>0.1606361060487229</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.04454070884138354</v>
+        <v>-0.1493212097301101</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
@@ -2066,25 +2066,25 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.07767435644122946</v>
+        <v>-0.03452737038032296</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1389940447226094</v>
+        <v>0.236110290034367</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.1739057312342586</v>
+        <v>-0.009382900406513326</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,46 +2093,46 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.0466153331720149</v>
+        <v>0.02522060355718684</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.05777807451534921</v>
+        <v>0.06934863678063345</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.08780219215488043</v>
+        <v>-0.1261519206299392</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.07227165179431035</v>
+        <v>0.1282340057329176</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07388716353878021</v>
+        <v>0.4936168437945803</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,25 +2718,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0141717447996648</v>
+        <v>0.05551586701082299</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0288104477691301</v>
+        <v>-0.2414396650489136</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02838974112164897</v>
+        <v>0.2820421701998607</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,40 +2745,40 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.007006899065950331</v>
+        <v>-0.04299136433173667</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02034494688762186</v>
+        <v>-0.2006903548373362</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003207426028255825</v>
+        <v>0.1837746133703574</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006248657574892328</v>
+        <v>-0.1543522925079109</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002342800815557814</v>
+        <v>-0.03492500492167466</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2790,79 +2790,79 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01502661393048315</v>
+        <v>0.02786372798752051</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02400958917916184</v>
+        <v>-0.310354441997835</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00112415518297495</v>
+        <v>-0.000837643414145372</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.004379945983964756</v>
+        <v>0.2235066648300265</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.0107430326722887</v>
+        <v>0.1253738319836764</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01774333591300801</v>
+        <v>-0.1447044677449079</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.08235485974769058</v>
+        <v>0.9173011440949848</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.004610945355186407</v>
+        <v>-0.1994028427361483</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005966904268427781</v>
+        <v>-0.211731703328831</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03343314225178473</v>
+        <v>-0.03926249529111744</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,25 +2880,25 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02011795153918684</v>
+        <v>-0.07522557291777775</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.04935756212806649</v>
+        <v>-0.1586552214707025</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03105090823141294</v>
+        <v>0.04682506074512637</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,13 +2907,13 @@
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02664615539699716</v>
+        <v>0.1198044286637819</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.005038896263161241</v>
+        <v>0.135662098558752</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0300067164309705</v>
+        <v>0.4298662480690543</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,43 +2934,43 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.004124662659737321</v>
+        <v>-0.005725077753720755</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004159189578353859</v>
+        <v>-0.2784648533327388</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01974696210371813</v>
+        <v>-0.266883055565073</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0004347217090593042</v>
+        <v>-0.05558941272613765</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01905846306042286</v>
+        <v>0.199689961063344</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,106 +2979,106 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01258484887888458</v>
+        <v>-0.238981839579549</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.007313188534045675</v>
+        <v>0.09311063341602747</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.00224355045054758</v>
+        <v>0.008301125095228947</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01492600680608253</v>
+        <v>-0.2459947020432721</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.003829499045662475</v>
+        <v>-0.04681013619634984</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01832493880225704</v>
+        <v>0.2171280032683686</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.005466688445090274</v>
+        <v>-0.04867284988966423</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02396824458529032</v>
+        <v>-0.145869899500718</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.004172005679171958</v>
+        <v>0.05694023097771487</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003608412693284221</v>
+        <v>-0.1052685328392949</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0002445450216749649</v>
+        <v>-0.01765487381758854</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.006232791323221483</v>
+        <v>-0.006884426439174628</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,49 +3087,49 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01365031245837751</v>
+        <v>0.04747929946279456</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.0313179586632102</v>
+        <v>-0.003614643010800851</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0001259619733323168</v>
+        <v>0.1634957709217714</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01607102120457339</v>
+        <v>-0.08393990120278941</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0009718372718214855</v>
+        <v>-0.1360910827810494</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01150428676812673</v>
+        <v>0.07042770003937636</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01549677501729317</v>
+        <v>-0.153143608548903</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,52 +3150,52 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.008307000016785811</v>
+        <v>-0.1855991665865628</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.004714618752294015</v>
+        <v>0.06910072750767995</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01811974302669769</v>
+        <v>-0.2761412025221334</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.003886252277332868</v>
+        <v>-0.08837224519780114</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02036555506717335</v>
+        <v>0.1843507096757481</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.004498922257989581</v>
+        <v>-0.2649951651063477</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,70 +3204,70 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02621416646370547</v>
+        <v>0.06456172435580759</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0194567601979027</v>
+        <v>0.2856776864030258</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.001593483290088892</v>
+        <v>-0.02997379198639199</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0006294771633811876</v>
+        <v>-0.003412284039637023</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.007280703038860276</v>
+        <v>0.1609556586251178</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02723737104018058</v>
+        <v>-0.1022934243274434</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.004785294937264746</v>
+        <v>0.1117438563314378</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1381008821413305</v>
+        <v>0.461844266741912</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01398827873620457</v>
+        <v>0.01658413167368952</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09572866747409403</v>
+        <v>-0.2495191489291213</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06784071283693728</v>
+        <v>0.3297609970446339</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.006918095895911656</v>
+        <v>-0.05293377328220761</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0689944289580823</v>
+        <v>-0.1873727862847769</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0</v>
@@ -3332,46 +3332,46 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01167136781555521</v>
+        <v>0.1488989462740125</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01195225718677575</v>
+        <v>-0.1705492621610323</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.005642782042439368</v>
+        <v>-0.03623620256103131</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02597815250404285</v>
+        <v>0.0932094096693722</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01911449586286601</v>
+        <v>-0.2960286272508294</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.002245430356996549</v>
+        <v>-0.1072582101360564</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02403754681358587</v>
+        <v>0.1962897030284999</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.000259284990164806</v>
+        <v>0.1112320425494206</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.03932477940839038</v>
+        <v>-0.1359316989870654</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.147786030807902</v>
+        <v>0.7440028745776951</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.006163879984179216</v>
+        <v>-0.2148628557129936</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.08074198143712258</v>
+        <v>-0.2410356340325725</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.05836677897635255</v>
+        <v>-0.0117113300985839</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0399649954720321</v>
+        <v>-0.09434481136121495</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.07966845522310785</v>
+        <v>-0.2227310786262786</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
@@ -3461,28 +3461,28 @@
         <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05186674826513343</v>
+        <v>0.05026495778617871</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02683565442064695</v>
+        <v>0.117519990092683</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.002119205177757018</v>
+        <v>0.05905377682496751</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.05498766095736696</v>
+        <v>0.3629169633621047</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.002482074509836902</v>
+        <v>-0.05573855279647101</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.02450828240155205</v>
+        <v>-0.1721991121534836</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.03600975489861988</v>
+        <v>-0.2460185250107627</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00215493584390315</v>
+        <v>-0.02822792693502324</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.03893896496230512</v>
+        <v>0.1647060054739684</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,73 +3548,73 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.02170316389033716</v>
+        <v>-0.2402472777386282</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
         <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.009322486861813226</v>
+        <v>0.1193011285097275</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.005785699683496837</v>
+        <v>0.04698829808150303</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.02729455926140279</v>
+        <v>-0.2265528284840596</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.003890061416221269</v>
+        <v>-0.04055241414672366</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03886222845266411</v>
+        <v>0.1633354863026657</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01161070871940018</v>
+        <v>-0.06032189990864194</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.00533237135164718</v>
+        <v>-0.06083085253739902</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.004031256923012375</v>
+        <v>0.001236549384665623</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.006898984010103907</v>
+        <v>-0.07507582787394224</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001202246061600821</v>
+        <v>-0.05477521371714018</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.01409267270881694</v>
+        <v>0.1176806221062813</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,19 +3656,19 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.01440852751102766</v>
+        <v>0.04604041724220517</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.03189625654001364</v>
+        <v>0.1183849603867285</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.007468671337127056</v>
+        <v>0.09939808648504811</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,13 +3677,13 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.02313434828604915</v>
+        <v>-0.07585748336711942</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
@@ -3692,37 +3692,37 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005681620455850726</v>
+        <v>-0.06963726065123144</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02832980807784578</v>
+        <v>0.0660967299997864</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.02553322888942734</v>
+        <v>-0.1091556605138885</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.012016292862219</v>
+        <v>-0.08249775917829315</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02288726616151082</v>
+        <v>0.1446999248924977</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,40 +3731,40 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.03039119344941865</v>
+        <v>-0.2576371652163599</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.003226810716905345</v>
+        <v>-0.06287293522681392</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03825915489089918</v>
+        <v>0.133464749105798</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01530162531834849</v>
+        <v>-0.3080922671229658</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,64 +3773,64 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02260446352540697</v>
+        <v>0.1167655375331608</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02302286987969983</v>
+        <v>0.273082031638717</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.006205959870159494</v>
+        <v>-0.04834540092342954</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.002766836911735763</v>
+        <v>0.001828443302222537</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02279735223648651</v>
+        <v>0.1312288428301928</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02963664023260407</v>
+        <v>-0.05242891010962882</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.004036107455184028</v>
+        <v>0.03581262735916998</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -4416,265 +4416,265 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3208916208819244</v>
+        <v>0.5070594854974348</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1163431041176946</v>
+        <v>-0.08504451812674586</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06487482427222858</v>
+        <v>-0.02224761472387065</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.156764072141536</v>
+        <v>-0.1157524701160362</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.219548707335111</v>
+        <v>0.4818942710625743</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08799137320255879</v>
+        <v>-0.160957767860414</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03367975009408868</v>
+        <v>-0.09136565302084473</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1069297419698214</v>
+        <v>-0.05397912216535049</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0528005409062066</v>
+        <v>0.1268482426813632</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.02446435983155037</v>
+        <v>-0.1314967751067522</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02866038147579631</v>
+        <v>-0.1305911198235127</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01683880565583108</v>
+        <v>-0.00872167993911944</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01411203111161188</v>
+        <v>0.01118102615856042</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04796196657449078</v>
+        <v>-0.2700943956929857</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.006460755628684671</v>
+        <v>-0.2030708057305584</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.03025403137563325</v>
+        <v>-0.06217838429295218</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01801556336749138</v>
+        <v>0.2307094641697861</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.03255825517132443</v>
+        <v>-0.08226527871472546</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.004462044340858105</v>
+        <v>0.07145294485817721</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05640348252828081</v>
+        <v>-0.163931719494037</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3757620945132137</v>
+        <v>0.6739145256189697</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.02909351722110718</v>
+        <v>0.01022003198855631</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.03974744580126966</v>
+        <v>-0.2541303395583421</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.01905626718213818</v>
+        <v>-0.1413156589997346</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05153748371056031</v>
+        <v>-0.06498715308516392</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.04370206324806737</v>
+        <v>-0.1502139521952972</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.08715172733107708</v>
+        <v>-0.07532907131491942</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.1501252614045313</v>
+        <v>-0.05450087620234718</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.07111802025747448</v>
+        <v>0.05506080801188731</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.060095316002152</v>
+        <v>0.01124328994107042</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.06603210646361941</v>
+        <v>0.1425575212383878</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.008486281714154673</v>
+        <v>-0.00424562631913288</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.13518260288255</v>
+        <v>0.3249842644190324</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.01393371924335329</v>
+        <v>-0.05307955775709433</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01949643422165039</v>
+        <v>-0.07498199128350254</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.00336893830804614</v>
+        <v>-0.1150066249217</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.07136007163073095</v>
+        <v>-0.2108229804750938</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.01574906215017958</v>
+        <v>0.06270354222394092</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.005600670680825057</v>
+        <v>0.0341055441204622</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.06568677071516424</v>
+        <v>0.04599245778463251</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,298 +4686,298 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.02265942358741162</v>
+        <v>-0.1701578104011787</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.05126859147897774</v>
+        <v>0.1306341186457673</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.04231394710597701</v>
+        <v>0.1391311914685751</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.03476970752950347</v>
+        <v>0.07603943392483867</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.06310355206130844</v>
+        <v>-0.1828544827189851</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.03866465342481561</v>
+        <v>0.06389140080564633</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0001338474370195141</v>
+        <v>0.01857932071229898</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.07473517621893541</v>
+        <v>0.0483969747326672</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.00804940420421804</v>
+        <v>-0.02804932022016869</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1103226151052171</v>
+        <v>0.014820176576817</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.01225358673624319</v>
+        <v>0.2898654840767083</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.004812402496838903</v>
+        <v>-0.003798184836739563</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.04004749300721674</v>
+        <v>-0.1250326761161878</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.02831811162087007</v>
+        <v>0.01604744395361469</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01203873506595499</v>
+        <v>-0.06923615921434777</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.02274876869846225</v>
+        <v>0.06652335917436705</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01108826541019727</v>
+        <v>0.1363287845154489</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.006038228224133157</v>
+        <v>0.03624788932512778</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.04348706204088899</v>
+        <v>-0.06626411359683071</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.001664613684191568</v>
+        <v>-0.03861119954864092</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.1066475616341592</v>
+        <v>-0.06533814585403472</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0425792314473524</v>
+        <v>0.07963419625725961</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.05297235782210508</v>
+        <v>0.001437313538485284</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03551739946884803</v>
+        <v>0.003991020833647495</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03893262163894121</v>
+        <v>-0.06605540945448672</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.004613311483062365</v>
+        <v>-0.02834297655004713</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01117377528769775</v>
+        <v>-0.02338939921049627</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.09445192265913731</v>
+        <v>0.1361844080545338</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.05775602920956268</v>
+        <v>-0.2261002149473959</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0197893957783723</v>
+        <v>0.05763961743540046</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01219754613039524</v>
+        <v>0.01738798850059292</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.06056470334972061</v>
+        <v>0.03102422251916665</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.03357005643410819</v>
+        <v>-0.1023919026725243</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.05615655923337762</v>
+        <v>0.1021648627682147</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00709341619548931</v>
+        <v>0.02984673341194449</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02246563732265854</v>
+        <v>0.1277321956035096</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.002334125692857886</v>
+        <v>-0.1852054645855729</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.02065070263411322</v>
+        <v>0.274164188982821</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.005760793812386181</v>
+        <v>0.01047815702670177</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.008259463486815027</v>
+        <v>0.1031203858278582</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02468107746932895</v>
+        <v>-0.1401969196324653</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.02304858536215524</v>
+        <v>-0.09450319710859478</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.01280399858658448</v>
+        <v>-0.02191006977092581</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,10 +5551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.6857527549060642</v>
+        <v>-0.2583633417860902</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -5563,13 +5563,13 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.282342692016595</v>
+        <v>-0.0398668940929907</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9677722106386616</v>
+        <v>0.2628937771389445</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5578,22 +5578,22 @@
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3712410279014721</v>
+        <v>-0.1753761747644191</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03693816650173384</v>
+        <v>0.03476448466706715</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6535959303830449</v>
+        <v>0.1839760092029472</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5608,19 +5608,19 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1297433298824813</v>
+        <v>-0.1025351115599122</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.09469125495766917</v>
+        <v>-0.0006425454754551899</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.009066089204244208</v>
+        <v>-0.03162082657487063</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
@@ -5629,25 +5629,25 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1981600954753085</v>
+        <v>0.02472954545518445</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02795375978538767</v>
+        <v>0.1836806058591949</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1619843611287338</v>
+        <v>0.05396542589174899</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.1312082495265645</v>
+        <v>-0.1056526340787783</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1049959535863755</v>
+        <v>-0.09433892226975281</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2627520270525875</v>
+        <v>0.153033083568504</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,37 +5686,37 @@
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.4090411010607855</v>
+        <v>-0.3079260961080305</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.4138910426857901</v>
+        <v>0.08265440080399955</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.8385479528377904</v>
+        <v>0.1546677613915576</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.3555000221799223</v>
+        <v>0.08099175539142765</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
@@ -5725,25 +5725,25 @@
         <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.2411508285374766</v>
+        <v>0.1940318885617895</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.1830702261441711</v>
+        <v>0.1344338679191212</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.1320094677405788</v>
+        <v>0.01906670131300144</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.07623388974493546</v>
+        <v>-0.05239837870954855</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0.01715263760568906</v>
+        <v>-0.04021735686952029</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.2461729765363896</v>
+        <v>-0.2050396724987587</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
@@ -5779,25 +5779,25 @@
         <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.09784907031151183</v>
+        <v>-0.007606150504098261</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.3009032961132183</v>
+        <v>0.09606876053145703</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1793298598800277</v>
+        <v>0.1212016388140961</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,13 +5806,13 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.03626337440398359</v>
+        <v>-0.006994161010638468</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.1770126500669414</v>
+        <v>-0.09216944716290991</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK10" t="n">
         <v>-0</v>
@@ -5824,19 +5824,19 @@
         <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.04769379094571768</v>
+        <v>0.1047929433125816</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.223310558605744</v>
+        <v>-0.1906354379407732</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1184820249825426</v>
+        <v>-0.07020884613628176</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
@@ -5848,10 +5848,10 @@
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1416941413860369</v>
+        <v>0.1164438465948621</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.07774152007824621</v>
+        <v>-0.002988421372379994</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.2139234004177502</v>
+        <v>-0.09059426788720255</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
@@ -5872,55 +5872,55 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01403157085504124</v>
+        <v>-0.002071646985762004</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.2416128352117189</v>
+        <v>0.0734031446712332</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0327518616152679</v>
+        <v>-0.008065089907953012</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.08484444384000164</v>
+        <v>0.01255625205671837</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1085508709260845</v>
+        <v>0.03548588667522695</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.09917308294417782</v>
+        <v>-0.02403957970596777</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1487538142177853</v>
+        <v>7.075500156652039e-05</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.2630481211720918</v>
+        <v>0.04768819354377264</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.08243209473695506</v>
+        <v>0.003069441754497871</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -5953,25 +5953,25 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0881409872636597</v>
+        <v>0.04732001981369759</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.173601433660038</v>
+        <v>0.02195592089293784</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.1580440804945395</v>
+        <v>-0.02108485418202832</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
@@ -5980,40 +5980,40 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1196221781310832</v>
+        <v>0.1094558877089583</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.03975846032922047</v>
+        <v>0.08060430542290339</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.008482186453138623</v>
+        <v>0.1119794121657161</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1628829163669889</v>
+        <v>0.1333092310398285</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,13 +6022,13 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.07089715791729129</v>
+        <v>0.002990910271766694</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.2156362879254731</v>
+        <v>-0.07343290514482848</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.03088381235264586</v>
+        <v>0.1555459584130055</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,37 +6049,37 @@
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01569585759569336</v>
+        <v>-0.04635993038536577</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.213735448174478</v>
+        <v>-0.1041193082819837</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0290082368916118</v>
+        <v>0.1363108893833395</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1224649146716903</v>
+        <v>-0.01223443452411322</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.2740566712577648</v>
+        <v>-0.07189106500424075</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
@@ -6091,13 +6091,13 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.09196100203930981</v>
+        <v>0.08175806910931974</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0991844784232175</v>
+        <v>0.009493103872618751</v>
       </c>
       <c r="GE10" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1615270145243239</v>
+        <v>0.4797667405914107</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01070885593204947</v>
+        <v>-0.009133564751300335</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.109338184205044</v>
+        <v>-0.2177016651005572</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6147,10 +6147,10 @@
         <v>-0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1313595771340432</v>
+        <v>0.5852201125015042</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01423233274066237</v>
+        <v>-0.1297723944971974</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.08542934630389556</v>
+        <v>-0.1653457130048936</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01608143805511507</v>
+        <v>0.1101597280191836</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01293035623031042</v>
+        <v>0.01636199894587489</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01697241997376671</v>
+        <v>-0.08320802075104859</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02086425668764005</v>
+        <v>0.007141925829105581</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00979162612623757</v>
+        <v>-0.1064334383194103</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01124651029354235</v>
+        <v>0.03046788822858576</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01200990410812194</v>
+        <v>0.1451666511937916</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.01373836491737035</v>
+        <v>0.06334080485811022</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04603610050489747</v>
+        <v>-0.08893779296734011</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1205156136098539</v>
+        <v>0.5996349008017985</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01037817823874026</v>
+        <v>-0.2609639490716745</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.06637814200711938</v>
+        <v>-0.2369318839039459</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06211353379448325</v>
+        <v>-0.1665586041773112</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.03064754450802943</v>
+        <v>-0.004325984733476592</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.05766365572661862</v>
+        <v>-0.01190230471200147</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6309,22 +6309,22 @@
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04951820521882568</v>
+        <v>-0.01825145423621825</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0189495801351908</v>
+        <v>0.07393368009529079</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02205662667937231</v>
+        <v>0.03078643963866471</v>
       </c>
       <c r="BR11" t="n">
         <v>-0</v>
@@ -6336,22 +6336,22 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.06546481919370961</v>
+        <v>0.3624398595909631</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.006814837159236022</v>
+        <v>-0.02177775897574008</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.02667744258519817</v>
+        <v>-0.1214157553128597</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,25 +6366,25 @@
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03231734222428918</v>
+        <v>-0.1962541453608726</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.002928255885064448</v>
+        <v>0.02162816550569585</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0252885981059847</v>
+        <v>0.07295192589585875</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.02048746634610831</v>
+        <v>-0.09138331188091887</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.008975240605085295</v>
+        <v>0.09664925269089084</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.01050773088303282</v>
+        <v>0.04636506273882741</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02303516150055581</v>
+        <v>-0.1882433131732145</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.002769022068360684</v>
+        <v>0.0203702264910936</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02913340892886617</v>
+        <v>0.08525963949229554</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.003802235984910601</v>
+        <v>0.01009536960526744</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.003980028243718352</v>
+        <v>0.01489646826073432</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01414406217125437</v>
+        <v>0.0692855319979956</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6471,28 +6471,28 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0164731963523642</v>
+        <v>-0.06822885509277786</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.006881297641744024</v>
+        <v>-0.03591363780139042</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0096819660359576</v>
+        <v>0.09158519232172985</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.03380345539156918</v>
+        <v>-0.1314321999898786</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0100641543819336</v>
+        <v>0.05600578220350388</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.02091708712748185</v>
+        <v>-0.09427691784786556</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.01704889703282269</v>
+        <v>-0.1139903273968637</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.003523473553831674</v>
+        <v>-0.04005564808214564</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01315656354703524</v>
+        <v>0.01492391412253137</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.007227821269118876</v>
+        <v>0.08426187941483591</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.006206500387428888</v>
+        <v>-0.002660719894234581</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0008112407676890839</v>
+        <v>-0.04914456529835368</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,52 +6576,52 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02380634548904118</v>
+        <v>-0.2137255844726937</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.002230338076717429</v>
+        <v>0.0028963618112047</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03078160760470564</v>
+        <v>0.09053139576727857</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0001456555643304901</v>
+        <v>-0.09633551498023163</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02017983054091088</v>
+        <v>0.01216323090963714</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03040171119330937</v>
+        <v>0.07264014592881594</v>
       </c>
       <c r="FM11" t="n">
         <v>-0</v>
@@ -6636,7 +6636,7 @@
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.0142002610150063</v>
+        <v>-0.1659420297271451</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02719602968676991</v>
+        <v>-0.04128623731934875</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.00125106291737697</v>
+        <v>-0.00709956036204493</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01863188724123727</v>
+        <v>-0.1104038917543697</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.0368290068755822</v>
+        <v>0.0426152093146365</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.382928885619543</v>
+        <v>-0.4961863920060907</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2110272864058035</v>
+        <v>0.1567326105116253</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2301440186739231</v>
+        <v>0.06983692781384546</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
@@ -6713,22 +6713,22 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3035572416321162</v>
+        <v>-0.6254476511610683</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2354737311392041</v>
+        <v>0.304886567526668</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2620265469135719</v>
+        <v>0.1805777993113766</v>
       </c>
       <c r="O12" t="n">
         <v>-0</v>
@@ -6746,22 +6746,22 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09315726790477447</v>
+        <v>-0.06810487241496815</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02407302708056691</v>
+        <v>0.01886613514049642</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.03166680449154824</v>
+        <v>-0.002103362544693323</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6773,22 +6773,22 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1514367949087342</v>
+        <v>-0.0496823786823726</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.03866987463600772</v>
+        <v>0.1690699455237701</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.04518403326603113</v>
+        <v>-0.2788737545677176</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -6797,19 +6797,19 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.04283878780730673</v>
+        <v>-0.1794898514702752</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.03770660599512976</v>
+        <v>0.06071514713368366</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.06230830356608638</v>
+        <v>-0.2928077791654923</v>
       </c>
       <c r="AP12" t="n">
         <v>-0</v>
@@ -6827,52 +6827,52 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.2586053951175512</v>
+        <v>-0.2755520802394067</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.0002618281038161932</v>
+        <v>0.185333128620785</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.01233543447364582</v>
+        <v>0.0569411603017593</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.003841016644337887</v>
+        <v>0.0394131988987451</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.2128791500119624</v>
+        <v>-0.004234282371556552</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.2683607702882946</v>
+        <v>0.1422781488966285</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
         <v>-0</v>
@@ -6881,22 +6881,22 @@
         <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.1075470301764043</v>
+        <v>0.1496302649152298</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.02151637038000631</v>
+        <v>0.1227683010464339</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.09611209897645892</v>
+        <v>0.006039352181742033</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
@@ -6908,16 +6908,16 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.2049023328119819</v>
+        <v>-0.2049752587182118</v>
       </c>
       <c r="BW12" t="n">
         <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.007709078885674764</v>
+        <v>0.08021180039628857</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05245112025732594</v>
+        <v>0.01204226668740459</v>
       </c>
       <c r="BZ12" t="n">
         <v>-0</v>
@@ -6926,7 +6926,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.08408753311861007</v>
+        <v>0.2408781289855911</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.04554594983095449</v>
+        <v>-0.07887914248316112</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.006904445042509356</v>
+        <v>0.005303393747182267</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6962,25 +6962,25 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.02583128845473585</v>
+        <v>0.1397918449536206</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.08416205135136776</v>
+        <v>-0.1539690843285213</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.07601821158261084</v>
+        <v>-0.1079098011119705</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS12" t="n">
         <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU12" t="n">
         <v>0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.07537287230160822</v>
+        <v>0.2498429959067522</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>-0.05963315900854887</v>
+        <v>-0.07972169849108475</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.009517033292096353</v>
+        <v>-0.02406371620262775</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,19 +7016,19 @@
         <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.1503018251218754</v>
+        <v>0.1724599501309839</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0.05115648465885637</v>
+        <v>-0.02686514339165121</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.005517170473168108</v>
+        <v>0.0004801906620851312</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7037,22 +7037,22 @@
         <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.03812900830968702</v>
+        <v>0.1045867756875083</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03324956458991746</v>
+        <v>-0.06929821845153065</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.06428602715644711</v>
+        <v>0.05255871900847025</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>-0</v>
@@ -7070,22 +7070,22 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.08810745553789903</v>
+        <v>0.03434069471522218</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.07970864180737396</v>
+        <v>0.07037396103691673</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04652998628241064</v>
+        <v>-0.02444503207342992</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED12" t="n">
         <v>-0</v>
@@ -7097,22 +7097,22 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.04342146956249068</v>
+        <v>0.2839774353166377</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.02730459241025563</v>
+        <v>-0.05123467221408295</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.09584325332947176</v>
+        <v>-0.04151034220435001</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM12" t="n">
         <v>0</v>
@@ -7121,22 +7121,22 @@
         <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.008129794133924987</v>
+        <v>-0.1680528165161678</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03178802839586744</v>
+        <v>-0.04440263331868902</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03375619504440966</v>
+        <v>0.02189209900535474</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>-0</v>
@@ -7151,109 +7151,109 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.07745395619311647</v>
+        <v>0.278255659954341</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.05754074027670722</v>
+        <v>-0.09725144446372005</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01275628543885563</v>
+        <v>0.006834945172132289</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.06062429721940096</v>
+        <v>0.1016155940066093</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1007745534191185</v>
+        <v>0.1221649195677776</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04493885673272512</v>
+        <v>0.09520427966786345</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01863770796458284</v>
+        <v>0.2181525051187369</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03089415646377328</v>
+        <v>0.004886462187274376</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.006332542932650518</v>
+        <v>-0.09054229985198031</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.04866681256609156</v>
+        <v>0.2223244551364039</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.07294404210378624</v>
+        <v>-0.00160589128942235</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
         <v>0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6135510068133436</v>
+        <v>0.3731230966163772</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,16 +7270,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1404506949746929</v>
+        <v>-0.0420119052713564</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5437280686113877</v>
+        <v>-0.1519967645707042</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5917940231158141</v>
+        <v>0.5114096768604545</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0648661893165955</v>
+        <v>-0.1314644279615547</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5731938756302779</v>
+        <v>-0.2298414526665896</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04669978567041489</v>
+        <v>0.1059847255371112</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,16 +7324,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1130876964233671</v>
+        <v>-0.1239327724257471</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.02623702714297822</v>
+        <v>-0.003692964509654546</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.02737363489260893</v>
+        <v>-0.02481589348599168</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01984496662799161</v>
+        <v>-0.2852387921779427</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03840647895295112</v>
+        <v>0.005883904099942509</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.09886028423330699</v>
+        <v>0.03253196490208723</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0007080982819437974</v>
+        <v>-0.04508618354797846</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.09198813056478228</v>
+        <v>0.02148416880675669</v>
       </c>
       <c r="AQ13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4701366775181178</v>
+        <v>0.484734091313733</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.08134485938090293</v>
+        <v>-0.2618613294231842</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.2453207249888843</v>
+        <v>-0.100872759032485</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1271631773566036</v>
+        <v>-0.02740839907287607</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,52 +7432,52 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1573577979292298</v>
+        <v>-0.0170139464554738</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.2076775070160965</v>
+        <v>-0.07636416204772974</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1625169645857042</v>
+        <v>0.06583359639185188</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.0002840842913196296</v>
+        <v>0.08109149286247117</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01471145331143057</v>
+        <v>-0.0309351200133408</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.251002960807876</v>
+        <v>0.2604614951639241</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.07779324302853861</v>
+        <v>-0.08183622510665269</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1491167636114515</v>
+        <v>-0.09134239028764626</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,28 +7498,28 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.09619484982500481</v>
+        <v>-0.107958548985595</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.005983946974629257</v>
+        <v>0.03243570484548945</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1170353776268224</v>
+        <v>0.04958527758706763</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,100 +7531,100 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.002296844570857497</v>
+        <v>-0.1473096280980469</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01947688716757867</v>
+        <v>0.1250850613702314</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.0277333329366079</v>
+        <v>0.1024362216052699</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.078165653000103</v>
+        <v>-0.1091074693733954</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005119086727193778</v>
+        <v>0.01151657639985174</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1222148291313387</v>
+        <v>0.07038002457888469</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04419751000356991</v>
+        <v>-0.04681290746384328</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05595192738315061</v>
+        <v>-0.1707249654454656</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.0005220588020141033</v>
+        <v>0.04162489024834271</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.004190261860935802</v>
+        <v>-0.011396451084524</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03516335817717366</v>
+        <v>-0.05079057700530599</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.004427817906718794</v>
+        <v>0.0683773996895669</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.06729325639764951</v>
+        <v>-0.01679069389854348</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,25 +7648,25 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0216873409555569</v>
+        <v>-0.08180964000143437</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.06129247823312712</v>
+        <v>0.0356200324368383</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.1088098611398633</v>
+        <v>-0.03651482864839592</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,79 +7675,79 @@
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02372881658951496</v>
+        <v>0.02274182718972386</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1266764719776892</v>
+        <v>-0.009250132885407386</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.0306076746217494</v>
+        <v>-0.009917387067506004</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01671357210572858</v>
+        <v>-0.01136986722426154</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.08099446088262575</v>
+        <v>0.1187451900952809</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.07480155726387143</v>
+        <v>-0.1288599505061859</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.006526490977241166</v>
+        <v>0.002711634422247438</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1107535497989122</v>
+        <v>0.0391519035327915</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.001968857131267095</v>
+        <v>0.1979892506498809</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01099511333342135</v>
+        <v>-0.1015970407047229</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0574792873529761</v>
+        <v>0.1136250894637365</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,46 +7774,46 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.005449267358800503</v>
+        <v>0.009635546239645432</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.009599099906951195</v>
+        <v>-0.02707643154592556</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.03872360978027892</v>
+        <v>-0.04485091585740351</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.05366609501123285</v>
+        <v>-0.03023292655681834</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.05965625521377316</v>
+        <v>0.06345344347973311</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
